--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings_new.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings_new.xlsx
@@ -40,7 +40,7 @@
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz;. :，,可设置屏幕进入休眠状态的时间默认分钟一直处于常亮已完成运行过程中如若关闭此功能则在无操作自动熄灭</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。*请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢液界面图案万虹广场店济南楼宿舍豪酒桔子房共件束详情合计</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。*请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢液界面图案万虹广场店济南楼宿舍豪酒桔子房共件束详情合计起</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-— .￥¥℃•:：洗涤漂洗脱水暂停中打冷风烘干门锁开关管理员设置网络数据程序待机时间自投功能臭氧新风护理屏幕亮度声音控制语言系统升级恢复默认联系我们支付密码修改</t>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings_new.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings_new.xlsx
@@ -49,7 +49,7 @@
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz. :：请输入特殊出厂序列号</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!：:•大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网失败重新连接将在熄屏原输入两次不一致修改分钟消</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!：:•大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网失败重新连接将在熄屏原输入两次不一致修改分钟消烘干</t>
   </si>
   <si>
     <t>1234567890 :：</t>
